--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_15sep26_Tue.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_15sep26_Tue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED74BA3-5502-4AF9-9A10-36E94AE6F5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C23E380-A1B2-4589-AEA9-EA53D2CC1398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1130,7 +1130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1316,12 +1316,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1643,7 +1637,7 @@
     <col min="14" max="16384" width="8.81640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1687,35 +1681,37 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>2560</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-19.395465990000002</v>
+        <v>4.7497879559999996</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5">
-        <v>3176</v>
+        <v>2358</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="41"/>
+      <c r="J2" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
@@ -1723,36 +1719,40 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B2, $C$2:$C$760, C2, $D$2:$D$760, D2, $E$2:$E$760, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="10"/>
+      <c r="P2" s="25"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4">
-        <v>660</v>
+        <v>281</v>
       </c>
       <c r="F3" s="4">
-        <v>-16.624557859999999</v>
+        <v>4.5192486519999999</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="H3" s="5">
-        <v>791.6</v>
+        <v>268.85000000000002</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
@@ -1760,73 +1760,84 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B3, $C$2:$C$760, C3, $D$2:$D$760, D3, $E$2:$E$760, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>62</v>
+      <c r="O3" s="10"/>
+      <c r="P3" s="26"/>
+    </row>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>46267.375</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4">
-        <v>2660</v>
+        <v>20050</v>
       </c>
       <c r="F4" s="4">
-        <v>-16.24685139</v>
+        <v>4.2912873859999996</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H4" s="5">
-        <v>3176</v>
+        <v>19225</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" t="str">
+      <c r="J4" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="L4" s="18">
+        <v>20350</v>
+      </c>
+      <c r="M4" s="18">
+        <f>ABS((D4*E4)-L4)</f>
+        <v>300</v>
+      </c>
+      <c r="N4" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B4, $C$2:$C$760, C4, $D$2:$D$760, D4, $E$2:$E$760, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>62</v>
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>46252.645138888889</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4">
-        <v>3914</v>
+        <v>401</v>
       </c>
       <c r="F5" s="4">
-        <v>-15.014656390000001</v>
+        <v>4.1558441559999997</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="H5" s="5">
-        <v>4605.5</v>
+        <v>385</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="43" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="17"/>
@@ -1836,36 +1847,40 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B5, $C$2:$C$760, C5, $D$2:$D$760, D5, $E$2:$E$760, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4">
-        <v>196</v>
+        <v>2435</v>
       </c>
       <c r="F6" s="4">
-        <v>-14.559721010000001</v>
+        <v>3.26547922</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5">
-        <v>229.4</v>
+        <v>2358</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="41"/>
+      <c r="J6" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -1873,50 +1888,63 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B6, $C$2:$C$760, C6, $D$2:$D$760, D6, $E$2:$E$760, E6) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
-        <v>46252.688194444447</v>
+        <v>46275.457638888889</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E7" s="4">
-        <v>136.15</v>
+        <v>222</v>
       </c>
       <c r="F7" s="4">
-        <v>-14.50549451</v>
+        <v>3.2654200389999999</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5">
-        <v>159.25</v>
+        <v>214.98</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="41"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" t="str">
+      <c r="J7" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="L7" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M7" s="18">
+        <f>ABS((D7*E7)-L7)</f>
+        <v>34175</v>
+      </c>
+      <c r="N7" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B7, $C$2:$C$760, C7, $D$2:$D$760, D7, $E$2:$E$760, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>62</v>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -1925,21 +1953,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>2752</v>
+        <v>13552</v>
       </c>
       <c r="F8" s="4">
-        <v>-13.35012594</v>
+        <v>3.0100334449999999</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H8" s="5">
-        <v>3176</v>
+        <v>13156</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="41"/>
+      <c r="J8" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
@@ -1947,8 +1977,10 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B8, $C$2:$C$760, C8, $D$2:$D$760, D8, $E$2:$E$760, E8) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -1959,13 +1991,13 @@
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4">
-        <v>4014</v>
+        <v>4710</v>
       </c>
       <c r="F9" s="4">
-        <v>-12.84333949</v>
+        <v>2.269026164</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>98</v>
@@ -1976,7 +2008,9 @@
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="41"/>
+      <c r="J9" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
@@ -1985,51 +2019,58 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4">
-        <v>701</v>
+    <row r="10" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="29">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31">
+        <v>19550</v>
       </c>
       <c r="F10" s="4">
-        <v>-10.74611663</v>
+        <v>1.6905071519999999</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5">
-        <v>785.4</v>
+        <v>19225</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" t="str">
+      <c r="K10" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L10" s="27">
+        <v>19992</v>
+      </c>
+      <c r="M10" s="27">
+        <f>ABS((D10*E10)-L10)</f>
+        <v>442</v>
+      </c>
+      <c r="N10" s="28" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B10, $C$2:$C$760, C10, $D$2:$D$760, D10, $E$2:$E$760, E10) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="11" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>62</v>
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
@@ -2038,21 +2079,23 @@
         <v>100</v>
       </c>
       <c r="E11" s="4">
-        <v>111</v>
+        <v>391</v>
       </c>
       <c r="F11" s="4">
-        <v>-10.28853148</v>
+        <v>1.5584415579999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H11" s="5">
-        <v>123.73</v>
+        <v>385</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="41"/>
+      <c r="J11" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
@@ -2060,36 +2103,40 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B11, $C$2:$C$760, C11, $D$2:$D$760, D11, $E$2:$E$760, E11) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
-        <v>62</v>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4">
-        <v>4164</v>
+        <v>1666</v>
       </c>
       <c r="F12" s="4">
-        <v>-9.5863641299999998</v>
+        <v>1.4616321560000001</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H12" s="5">
-        <v>4605.5</v>
+        <v>1642</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="41"/>
+      <c r="J12" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -2098,30 +2145,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
-        <v>46252.635416666664</v>
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" s="4">
-        <v>2892</v>
+        <v>3888</v>
       </c>
       <c r="F13" s="4">
-        <v>-8.9420654909999993</v>
+        <v>1.2025612990000001</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H13" s="5">
-        <v>3176</v>
+        <v>3841.8</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
@@ -2134,105 +2181,129 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B13, $C$2:$C$760, C13, $D$2:$D$760, D13, $E$2:$E$760, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>62</v>
+      <c r="O13" s="26"/>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E14" s="4">
-        <v>1751</v>
+        <v>870</v>
       </c>
       <c r="F14" s="4">
-        <v>-7.4034902169999999</v>
+        <v>1.168672597</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H14" s="5">
-        <v>1891</v>
+        <v>859.95</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" t="str">
+      <c r="J14" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L14" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M14" s="18">
+        <f>ABS((D14*E14)-L14)</f>
+        <v>300</v>
+      </c>
+      <c r="N14" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B14, $C$2:$C$760, C14, $D$2:$D$760, D14, $E$2:$E$760, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>62</v>
+      <c r="O14" s="10"/>
+      <c r="P14" s="25"/>
+    </row>
+    <row r="15" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E15" s="4">
-        <v>115.25</v>
+        <v>205</v>
       </c>
       <c r="F15" s="4">
-        <v>-6.85363291</v>
+        <v>0.83620265620000001</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5">
-        <v>123.73</v>
+        <v>203.3</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="41"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" t="str">
+      <c r="J15" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M15" s="18">
+        <f>ABS((D15*E15)-L15)</f>
+        <v>300</v>
+      </c>
+      <c r="N15" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B15, $C$2:$C$760, C15, $D$2:$D$760, D15, $E$2:$E$760, E15) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3856</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.36961840800000001</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="4">
-        <v>116</v>
-      </c>
-      <c r="F16" s="4">
-        <v>-6.247474339</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="H16" s="5">
-        <v>123.73</v>
+        <v>3841.8</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
@@ -2245,77 +2316,79 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B16, $C$2:$C$760, C16, $D$2:$D$760, D16, $E$2:$E$760, E16) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
-        <v>46254.375</v>
+      <c r="O16" s="19"/>
+      <c r="P16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>2230</v>
+        <v>3830</v>
       </c>
       <c r="F17" s="4">
-        <v>-6.1052631579999996</v>
+        <v>-0.30714769120000002</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="H17" s="5">
-        <v>2375</v>
+        <v>3841.8</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>148</v>
-      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
-      <c r="N17" s="10" t="str">
+      <c r="N17" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B17, $C$2:$C$760, C17, $D$2:$D$760, D17, $E$2:$E$760, E17) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
-        <v>62</v>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="4">
-        <v>18052</v>
+        <v>1302</v>
       </c>
       <c r="F18" s="4">
-        <v>-6.1014304289999997</v>
+        <v>-0.4054157424</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H18" s="5">
-        <v>19225</v>
+        <v>1307.3</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="41"/>
+      <c r="J18" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
@@ -2324,67 +2397,78 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="19" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
-        <v>62</v>
+    <row r="19" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E19" s="4">
-        <v>4415</v>
+        <v>214</v>
       </c>
       <c r="F19" s="4">
-        <v>-5.7429547400000001</v>
+        <v>-0.45585635870000002</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="H19" s="5">
-        <v>4684</v>
+        <v>214.98</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="41"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" t="str">
+      <c r="J19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L19" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M19" s="18">
+        <f>ABS((D19*E19)-L19)</f>
+        <v>500</v>
+      </c>
+      <c r="N19" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B19, $C$2:$C$760, C19, $D$2:$D$760, D19, $E$2:$E$760, E19) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="E20" s="4">
-        <v>31.01</v>
+        <v>878</v>
       </c>
       <c r="F20" s="4">
-        <v>-5.5437100209999999</v>
+        <v>-0.5606206467</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H20" s="5">
-        <v>32.83</v>
+        <v>882.95</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
@@ -2399,14 +2483,15 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B20, $C$2:$C$760, C20, $D$2:$D$760, D20, $E$2:$E$760, E20) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O20" s="34"/>
-    </row>
-    <row r="21" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+    </row>
+    <row r="21" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
@@ -2415,21 +2500,21 @@
         <v>1</v>
       </c>
       <c r="E21" s="4">
-        <v>4364</v>
+        <v>4010</v>
       </c>
       <c r="F21" s="4">
-        <v>-5.2437303220000002</v>
+        <v>-0.74257425740000005</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5">
-        <v>4605.5</v>
+        <v>4040</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="42" t="s">
+      <c r="J21" s="41" t="s">
         <v>41</v>
       </c>
       <c r="K21" s="17"/>
@@ -2439,31 +2524,33 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B21, $C$2:$C$760, C21, $D$2:$D$760, D21, $E$2:$E$760, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="4">
-        <v>4456</v>
+        <v>3810</v>
       </c>
       <c r="F22" s="4">
-        <v>-4.8676345000000003</v>
+        <v>-0.82773699830000003</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H22" s="5">
-        <v>4684</v>
+        <v>3841.8</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
@@ -2476,77 +2563,70 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B22, $C$2:$C$760, C22, $D$2:$D$760, D22, $E$2:$E$760, E22) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3">
-        <v>46258.601388888892</v>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>2271</v>
+        <v>19052</v>
       </c>
       <c r="F23" s="4">
-        <v>-4.3789473680000004</v>
+        <v>-0.89986996100000005</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H23" s="5">
-        <v>2375</v>
+        <v>19225</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="L23" s="18">
-        <v>7113</v>
-      </c>
-      <c r="M23" s="18">
-        <f>ABS((D23*E23)-L23)</f>
-        <v>300</v>
-      </c>
-      <c r="N23" s="10" t="str">
+      <c r="J23" s="41"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B23, $C$2:$C$760, C23, $D$2:$D$760, D23, $E$2:$E$760, E23) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="24" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4">
-        <v>4410</v>
+        <v>4640</v>
       </c>
       <c r="F24" s="4">
-        <v>-4.2449245470000001</v>
+        <v>-0.93936806149999996</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H24" s="5">
-        <v>4605.5</v>
+        <v>4684</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
@@ -2559,13 +2639,14 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B24, $C$2:$C$760, C24, $D$2:$D$760, D24, $E$2:$E$760, E24) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
@@ -2574,21 +2655,21 @@
         <v>50</v>
       </c>
       <c r="E25" s="4">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F25" s="4">
-        <v>-4.1771327569999999</v>
+        <v>-1.1313330049999999</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H25" s="5">
-        <v>214.98</v>
+        <v>203.3</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="41" t="s">
+      <c r="J25" s="42" t="s">
         <v>41</v>
       </c>
       <c r="K25" s="17"/>
@@ -2599,122 +2680,125 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="26" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
-        <v>46274.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="4">
-        <v>1005</v>
+        <v>1142</v>
       </c>
       <c r="F26" s="4">
-        <v>-3.8277511959999999</v>
+        <v>-1.1341009440000001</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H26" s="5">
-        <v>1045</v>
+        <v>1155.0999999999999</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="L26" s="18">
-        <v>15600</v>
-      </c>
-      <c r="M26" s="18">
-        <f>ABS((D26*E26)-L26)</f>
-        <v>525</v>
-      </c>
-      <c r="N26" s="10" t="str">
+      <c r="J26" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B26, $C$2:$C$760, C26, $D$2:$D$760, D26, $E$2:$E$760, E26) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
     </row>
-    <row r="27" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>62</v>
+    <row r="27" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>46260.375</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E27" s="4">
-        <v>119</v>
+        <v>2348</v>
       </c>
       <c r="F27" s="4">
-        <v>-3.8228400549999999</v>
+        <v>-1.1368421049999999</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H27" s="5">
-        <v>123.73</v>
+        <v>2375</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="41"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
+      <c r="J27" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="L27" s="18">
+        <v>7344</v>
+      </c>
+      <c r="M27" s="18">
+        <f>ABS((D27*E27)-L27)</f>
+        <v>300</v>
+      </c>
       <c r="N27" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B27, $C$2:$C$760, C27, $D$2:$D$760, D27, $E$2:$E$760, E27) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O27" s="10"/>
       <c r="P27" s="10"/>
     </row>
-    <row r="28" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
-        <v>46252.6875</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E28" s="4">
-        <v>326</v>
+        <v>850</v>
       </c>
       <c r="F28" s="4">
-        <v>-3.6927621859999999</v>
+        <v>-1.157044014</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H28" s="5">
-        <v>338.5</v>
+        <v>859.95</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="41" t="s">
-        <v>41</v>
+      <c r="J28" s="42" t="s">
+        <v>55</v>
       </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
@@ -2723,36 +2807,39 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B28, $C$2:$C$760, C28, $D$2:$D$760, D28, $E$2:$E$760, E28) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E29" s="4">
-        <v>411</v>
+        <v>6920</v>
       </c>
       <c r="F29" s="4">
-        <v>-3.6116322699999999</v>
+        <v>-1.3542409120000001</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H29" s="5">
-        <v>426.4</v>
+        <v>7015</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="41"/>
+      <c r="J29" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -2761,12 +2848,12 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="30" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
@@ -2775,16 +2862,16 @@
         <v>50</v>
       </c>
       <c r="E30" s="4">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F30" s="4">
-        <v>-3.5907525819999999</v>
+        <v>-1.3861754580000001</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H30" s="5">
-        <v>203.3</v>
+        <v>214.98</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
@@ -2799,36 +2886,40 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B30, $C$2:$C$760, C30, $D$2:$D$760, D30, $E$2:$E$760, E30) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
-        <v>62</v>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E31" s="4">
-        <v>18552</v>
+        <v>122</v>
       </c>
       <c r="F31" s="4">
-        <v>-3.500650195</v>
+        <v>-1.398205771</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="H31" s="5">
-        <v>19225</v>
+        <v>123.73</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="41"/>
+      <c r="J31" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
@@ -2836,84 +2927,87 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B31, $C$2:$C$760, C31, $D$2:$D$760, D31, $E$2:$E$760, E31) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+    </row>
+    <row r="32" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
-        <v>46121.375</v>
+        <v>46280.375902777778</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E32" s="4">
-        <v>1614</v>
+        <v>2230</v>
       </c>
       <c r="F32" s="4">
-        <v>-3.260608967</v>
+        <v>-1.423393157</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="H32" s="5">
-        <v>1668.4</v>
+        <v>2262.1999999999998</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="L32" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
+        <v>20880</v>
       </c>
       <c r="M32" s="18">
         <f>ABS((D32*E32)-L32)</f>
-        <v>540</v>
+        <v>810</v>
       </c>
       <c r="N32" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B32, $C$2:$C$760, C32, $D$2:$D$760, D32, $E$2:$E$760, E32) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+    </row>
+    <row r="33" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E33" s="4">
-        <v>561</v>
+        <v>401</v>
       </c>
       <c r="F33" s="4">
-        <v>-3.2508407350000001</v>
+        <v>-1.595092025</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="H33" s="5">
-        <v>579.85</v>
+        <v>407.5</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="41" t="s">
-        <v>41</v>
+      <c r="J33" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
@@ -2922,126 +3016,115 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B33, $C$2:$C$760, C33, $D$2:$D$760, D33, $E$2:$E$760, E33) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3">
-        <v>46269.375</v>
+      <c r="P33" s="10"/>
+    </row>
+    <row r="34" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4">
-        <v>3210</v>
+        <v>1614</v>
       </c>
       <c r="F34" s="4">
-        <v>-3.079710145</v>
+        <v>-1.7052375150000001</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="H34" s="5">
-        <v>3312</v>
+        <v>1642</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J34" s="24" t="s">
+      <c r="J34" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="L34" s="18">
-        <v>6880</v>
-      </c>
-      <c r="M34" s="27">
-        <f>ABS((D34*E34)-L34)</f>
-        <v>460</v>
-      </c>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
       <c r="N34" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B34, $C$2:$C$760, C34, $D$2:$D$760, D34, $E$2:$E$760, E34) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P34" s="10"/>
-    </row>
-    <row r="35" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
-        <v>46031.4375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="4">
-        <v>1052</v>
+        <v>1132</v>
       </c>
       <c r="F35" s="4">
-        <v>-3.0414746539999999</v>
+        <v>-1.999826855</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="H35" s="5">
-        <v>1085</v>
+        <v>1155.0999999999999</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="24" t="s">
+      <c r="J35" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="M35" s="18">
-        <f>ABS((D35*E35)-L35)</f>
-        <v>3156</v>
-      </c>
-      <c r="N35" s="10" t="str">
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B35, $C$2:$C$760, C35, $D$2:$D$760, D35, $E$2:$E$760, E35) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P35" s="19"/>
-    </row>
-    <row r="36" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3">
-        <v>46252.688194444447</v>
+    </row>
+    <row r="36" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="4">
-        <v>640</v>
+        <v>3760</v>
       </c>
       <c r="F36" s="4">
-        <v>-3.015608426</v>
+        <v>-2.1292102659999999</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="H36" s="5">
-        <v>659.9</v>
+        <v>3841.8</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J36" s="41"/>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
@@ -3050,39 +3133,36 @@
         <v>Unique</v>
       </c>
       <c r="O36"/>
-      <c r="P36"/>
-    </row>
-    <row r="37" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="4">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="E37" s="4">
-        <v>836</v>
+        <v>1277</v>
       </c>
       <c r="F37" s="4">
-        <v>-2.785045642</v>
+        <v>-2.3177541499999998</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H37" s="5">
-        <v>859.95</v>
+        <v>1307.3</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="41" t="s">
-        <v>118</v>
-      </c>
+      <c r="J37" s="41"/>
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
@@ -3093,35 +3173,37 @@
       <c r="O37"/>
       <c r="P37"/>
     </row>
-    <row r="38" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E38" s="4">
-        <v>4560</v>
+        <v>862</v>
       </c>
       <c r="F38" s="4">
-        <v>-2.6473099910000002</v>
+        <v>-2.3727277880000002</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="H38" s="5">
-        <v>4684</v>
+        <v>882.95</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="41"/>
+      <c r="J38" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
@@ -3132,37 +3214,35 @@
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E39" s="4">
-        <v>862</v>
+        <v>4560</v>
       </c>
       <c r="F39" s="4">
-        <v>-2.3727277880000002</v>
+        <v>-2.6473099910000002</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="H39" s="5">
-        <v>882.95</v>
+        <v>4684</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J39" s="41"/>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -3173,35 +3253,37 @@
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="4">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E40" s="4">
-        <v>1277</v>
+        <v>836</v>
       </c>
       <c r="F40" s="4">
-        <v>-2.3177541499999998</v>
+        <v>-2.785045642</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H40" s="5">
-        <v>1307.3</v>
+        <v>859.95</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="41"/>
+      <c r="J40" s="41" t="s">
+        <v>118</v>
+      </c>
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
@@ -3212,35 +3294,37 @@
       <c r="O40"/>
       <c r="P40"/>
     </row>
-    <row r="41" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
-        <v>62</v>
+    <row r="41" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E41" s="4">
-        <v>3760</v>
+        <v>640</v>
       </c>
       <c r="F41" s="4">
-        <v>-2.1292102659999999</v>
+        <v>-3.015608426</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="H41" s="5">
-        <v>3841.8</v>
+        <v>659.9</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="41"/>
+      <c r="J41" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
@@ -3249,117 +3333,126 @@
         <v>Unique</v>
       </c>
       <c r="O41"/>
-    </row>
-    <row r="42" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P41"/>
+    </row>
+    <row r="42" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
-        <v>46252.635416666664</v>
+        <v>46031.4375</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="4">
-        <v>1132</v>
+        <v>1052</v>
       </c>
       <c r="F42" s="4">
-        <v>-1.999826855</v>
+        <v>-3.0414746539999999</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="H42" s="5">
-        <v>1155.0999999999999</v>
+        <v>1085</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J42" s="41" t="s">
+      <c r="J42" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" t="str">
+      <c r="M42" s="18">
+        <f>ABS((D42*E42)-L42)</f>
+        <v>3156</v>
+      </c>
+      <c r="N42" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B42, $C$2:$C$760, C42, $D$2:$D$760, D42, $E$2:$E$760, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="6" t="s">
-        <v>62</v>
+      <c r="P42" s="19"/>
+    </row>
+    <row r="43" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
+        <v>46269.375</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
-        <v>1614</v>
+        <v>3210</v>
       </c>
       <c r="F43" s="4">
-        <v>-1.7052375150000001</v>
+        <v>-3.079710145</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H43" s="5">
-        <v>1642</v>
+        <v>3312</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="22" t="s">
+      <c r="J43" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
+      <c r="K43" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="L43" s="18">
+        <v>6880</v>
+      </c>
+      <c r="M43" s="27">
+        <f>ABS((D43*E43)-L43)</f>
+        <v>460</v>
+      </c>
       <c r="N43" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B43, $C$2:$C$760, C43, $D$2:$D$760, D43, $E$2:$E$760, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O43"/>
-      <c r="P43"/>
-    </row>
-    <row r="44" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E44" s="4">
-        <v>401</v>
+        <v>561</v>
       </c>
       <c r="F44" s="4">
-        <v>-1.595092025</v>
+        <v>-3.2508407350000001</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="H44" s="5">
-        <v>407.5</v>
+        <v>579.85</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="22" t="s">
-        <v>55</v>
+      <c r="J44" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
@@ -3369,84 +3462,86 @@
         <v>Unique</v>
       </c>
       <c r="O44"/>
-    </row>
-    <row r="45" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44"/>
+    </row>
+    <row r="45" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
-        <v>46280.375902777778</v>
+        <v>46121.375</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E45" s="4">
-        <v>2230</v>
+        <v>1614</v>
       </c>
       <c r="F45" s="4">
-        <v>-1.423393157</v>
+        <v>-3.260608967</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="H45" s="5">
-        <v>2262.1999999999998</v>
+        <v>1668.4</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J45" s="24" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K45" s="18" t="s">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="L45" s="18">
-        <v>20880</v>
+        <f>3*1794</f>
+        <v>5382</v>
       </c>
       <c r="M45" s="18">
         <f>ABS((D45*E45)-L45)</f>
-        <v>810</v>
+        <v>540</v>
       </c>
       <c r="N45" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B45, $C$2:$C$760, C45, $D$2:$D$760, D45, $E$2:$E$760, E45) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="3">
-        <v>46252.6875</v>
+      <c r="O45"/>
+      <c r="P45"/>
+    </row>
+    <row r="46" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4">
-        <v>122</v>
+        <v>18552</v>
       </c>
       <c r="F46" s="4">
-        <v>-1.398205771</v>
+        <v>-3.500650195</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="H46" s="5">
-        <v>123.73</v>
+        <v>19225</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="42" t="s">
-        <v>41</v>
-      </c>
+      <c r="J46" s="41"/>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
@@ -3454,15 +3549,15 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B46, $C$2:$C$760, C46, $D$2:$D$760, D46, $E$2:$E$760, E46) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-    </row>
-    <row r="47" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O46"/>
+      <c r="P46"/>
+    </row>
+    <row r="47" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
@@ -3471,16 +3566,16 @@
         <v>50</v>
       </c>
       <c r="E47" s="4">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="F47" s="4">
-        <v>-1.3861754580000001</v>
+        <v>-3.5907525819999999</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H47" s="5">
-        <v>214.98</v>
+        <v>203.3</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
@@ -3495,38 +3590,38 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B47, $C$2:$C$760, C47, $D$2:$D$760, D47, $E$2:$E$760, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O47"/>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E48" s="4">
-        <v>6920</v>
+        <v>411</v>
       </c>
       <c r="F48" s="4">
-        <v>-1.3542409120000001</v>
+        <v>-3.6116322699999999</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H48" s="5">
-        <v>7015</v>
+        <v>426.4</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="22" t="s">
-        <v>140</v>
-      </c>
+      <c r="J48" s="41"/>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
@@ -3537,36 +3632,36 @@
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
-        <v>46252.635416666664</v>
+        <v>46252.6875</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E49" s="4">
-        <v>850</v>
+        <v>326</v>
       </c>
       <c r="F49" s="4">
-        <v>-1.157044014</v>
+        <v>-3.6927621859999999</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H49" s="5">
-        <v>859.95</v>
+        <v>338.5</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="42" t="s">
-        <v>55</v>
+      <c r="J49" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
@@ -3575,99 +3670,99 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B49, $C$2:$C$760, C49, $D$2:$D$760, D49, $E$2:$E$760, E49) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="3">
-        <v>46260.375</v>
+    <row r="50" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E50" s="4">
-        <v>2348</v>
+        <v>119</v>
       </c>
       <c r="F50" s="4">
-        <v>-1.1368421049999999</v>
+        <v>-3.8228400549999999</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H50" s="5">
-        <v>2375</v>
+        <v>123.73</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="L50" s="18">
-        <v>7344</v>
-      </c>
-      <c r="M50" s="18">
-        <f>ABS((D50*E50)-L50)</f>
-        <v>300</v>
-      </c>
+      <c r="J50" s="41"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
       <c r="N50" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B50, $C$2:$C$760, C50, $D$2:$D$760, D50, $E$2:$E$760, E50) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O50"/>
+    </row>
+    <row r="51" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
-        <v>46252.635416666664</v>
+        <v>46274.375</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E51" s="4">
-        <v>1142</v>
+        <v>1005</v>
       </c>
       <c r="F51" s="4">
-        <v>-1.1341009440000001</v>
+        <v>-3.8277511959999999</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="H51" s="5">
-        <v>1155.0999999999999</v>
+        <v>1045</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" t="str">
+      <c r="J51" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="L51" s="18">
+        <v>15600</v>
+      </c>
+      <c r="M51" s="18">
+        <f>ABS((D51*E51)-L51)</f>
+        <v>525</v>
+      </c>
+      <c r="N51" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B51, $C$2:$C$760, C51, $D$2:$D$760, D51, $E$2:$E$760, E51) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
@@ -3676,21 +3771,21 @@
         <v>50</v>
       </c>
       <c r="E52" s="4">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F52" s="4">
-        <v>-1.1313330049999999</v>
+        <v>-4.1771327569999999</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H52" s="5">
-        <v>203.3</v>
+        <v>214.98</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="42" t="s">
+      <c r="J52" s="41" t="s">
         <v>41</v>
       </c>
       <c r="K52" s="17"/>
@@ -3703,30 +3798,30 @@
       <c r="O52"/>
       <c r="P52"/>
     </row>
-    <row r="53" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="4">
-        <v>4640</v>
+        <v>4410</v>
       </c>
       <c r="F53" s="4">
-        <v>-0.93936806149999996</v>
+        <v>-4.2449245470000001</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H53" s="5">
-        <v>4684</v>
+        <v>4605.5</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>8</v>
@@ -3739,71 +3834,81 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B53, $C$2:$C$760, C53, $D$2:$D$760, D53, $E$2:$E$760, E53) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="6" t="s">
-        <v>62</v>
+    <row r="54" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="3">
+        <v>46258.601388888892</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" s="4">
-        <v>19052</v>
+        <v>2271</v>
       </c>
       <c r="F54" s="4">
-        <v>-0.89986996100000005</v>
+        <v>-4.3789473680000004</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H54" s="5">
-        <v>19225</v>
+        <v>2375</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="41"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" t="str">
+      <c r="J54" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="L54" s="18">
+        <v>7113</v>
+      </c>
+      <c r="M54" s="18">
+        <f>ABS((D54*E54)-L54)</f>
+        <v>300</v>
+      </c>
+      <c r="N54" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B54, $C$2:$C$760, C54, $D$2:$D$760, D54, $E$2:$E$760, E54) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4">
-        <v>3810</v>
+        <v>4456</v>
       </c>
       <c r="F55" s="4">
-        <v>-0.82773699830000003</v>
+        <v>-4.8676345000000003</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H55" s="5">
-        <v>3841.8</v>
+        <v>4684</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
@@ -3816,13 +3921,15 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B55, $C$2:$C$760, C55, $D$2:$D$760, D55, $E$2:$E$760, E55) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O55"/>
+      <c r="P55"/>
+    </row>
+    <row r="56" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
@@ -3831,21 +3938,21 @@
         <v>1</v>
       </c>
       <c r="E56" s="4">
-        <v>4010</v>
+        <v>4364</v>
       </c>
       <c r="F56" s="4">
-        <v>-0.74257425740000005</v>
+        <v>-5.2437303220000002</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H56" s="5">
-        <v>4040</v>
+        <v>4605.5</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="41" t="s">
+      <c r="J56" s="42" t="s">
         <v>41</v>
       </c>
       <c r="K56" s="17"/>
@@ -3855,31 +3962,33 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B56, $C$2:$C$760, C56, $D$2:$D$760, D56, $E$2:$E$760, E56) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O56"/>
+      <c r="P56"/>
+    </row>
+    <row r="57" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="4">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E57" s="4">
-        <v>878</v>
+        <v>31.01</v>
       </c>
       <c r="F57" s="4">
-        <v>-0.5606206467</v>
+        <v>-5.5437100209999999</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H57" s="5">
-        <v>882.95</v>
+        <v>32.83</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
@@ -3894,84 +4003,77 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B57, $C$2:$C$760, C57, $D$2:$D$760, D57, $E$2:$E$760, E57) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3">
-        <v>46268.385416666664</v>
+      <c r="O57" s="34"/>
+      <c r="P57"/>
+    </row>
+    <row r="58" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E58" s="4">
-        <v>214</v>
+        <v>4415</v>
       </c>
       <c r="F58" s="4">
-        <v>-0.45585635870000002</v>
+        <v>-5.7429547400000001</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="H58" s="5">
-        <v>214.98</v>
+        <v>4684</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K58" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="L58" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M58" s="18">
-        <f>ABS((D58*E58)-L58)</f>
-        <v>500</v>
-      </c>
-      <c r="N58" s="10" t="str">
+      <c r="J58" s="41"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B58, $C$2:$C$760, C58, $D$2:$D$760, D58, $E$2:$E$760, E58) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3">
-        <v>46252.635416666664</v>
+      <c r="O58"/>
+      <c r="P58"/>
+    </row>
+    <row r="59" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>1302</v>
+        <v>18052</v>
       </c>
       <c r="F59" s="4">
-        <v>-0.4054157424</v>
+        <v>-6.1014304289999997</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H59" s="5">
-        <v>1307.3</v>
+        <v>19225</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J59" s="41"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
@@ -3982,67 +4084,73 @@
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="6" t="s">
-        <v>62</v>
+    <row r="60" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="3">
+        <v>46254.375</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E60" s="4">
-        <v>3830</v>
+        <v>2230</v>
       </c>
       <c r="F60" s="4">
-        <v>-0.30714769120000002</v>
+        <v>-6.1052631579999996</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="H60" s="5">
-        <v>3841.8</v>
+        <v>2375</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="41"/>
-      <c r="K60" s="17"/>
+      <c r="J60" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>148</v>
+      </c>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
-      <c r="N60" t="str">
+      <c r="N60" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B60, $C$2:$C$760, C60, $D$2:$D$760, D60, $E$2:$E$760, E60) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O60"/>
+      <c r="P60"/>
+    </row>
+    <row r="61" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E61" s="4">
-        <v>3856</v>
+        <v>116</v>
       </c>
       <c r="F61" s="4">
-        <v>0.36961840800000001</v>
+        <v>-6.247474339</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H61" s="5">
-        <v>3841.8</v>
+        <v>123.73</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
@@ -4055,127 +4163,111 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B61, $C$2:$C$760, C61, $D$2:$D$760, D61, $E$2:$E$760, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O61" s="19"/>
-    </row>
-    <row r="62" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="3">
-        <v>46261.375</v>
+      <c r="O61"/>
+      <c r="P61"/>
+    </row>
+    <row r="62" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E62" s="4">
-        <v>205</v>
+        <v>115.25</v>
       </c>
       <c r="F62" s="4">
-        <v>0.83620265620000001</v>
+        <v>-6.85363291</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H62" s="5">
-        <v>203.3</v>
+        <v>123.73</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K62" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="L62" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M62" s="18">
-        <f>ABS((D62*E62)-L62)</f>
-        <v>300</v>
-      </c>
-      <c r="N62" s="10" t="str">
+      <c r="J62" s="41"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B62, $C$2:$C$760, C62, $D$2:$D$760, D62, $E$2:$E$760, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-    </row>
-    <row r="63" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3">
-        <v>46261.375</v>
+      <c r="O62"/>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E63" s="4">
-        <v>870</v>
+        <v>1751</v>
       </c>
       <c r="F63" s="4">
-        <v>1.168672597</v>
+        <v>-7.4034902169999999</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="H63" s="5">
-        <v>859.95</v>
+        <v>1891</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K63" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="L63" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M63" s="18">
-        <f>ABS((D63*E63)-L63)</f>
-        <v>300</v>
-      </c>
-      <c r="N63" s="10" t="str">
+      <c r="J63" s="41"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B63, $C$2:$C$760, C63, $D$2:$D$760, D63, $E$2:$E$760, E63) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P63" s="25"/>
-    </row>
-    <row r="64" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="6" t="s">
-        <v>62</v>
+      <c r="O63"/>
+      <c r="P63"/>
+    </row>
+    <row r="64" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D64" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4">
-        <v>3888</v>
+        <v>2892</v>
       </c>
       <c r="F64" s="4">
-        <v>1.2025612990000001</v>
+        <v>-8.9420654909999993</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H64" s="5">
-        <v>3841.8</v>
+        <v>3176</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>8</v>
@@ -4188,39 +4280,38 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B64, $C$2:$C$760, C64, $D$2:$D$760, D64, $E$2:$E$760, E64) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O64" s="26"/>
-    </row>
-    <row r="65" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="3">
-        <v>46252.6875</v>
+      <c r="O64"/>
+      <c r="P64"/>
+    </row>
+    <row r="65" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E65" s="4">
-        <v>1666</v>
+        <v>4164</v>
       </c>
       <c r="F65" s="4">
-        <v>1.4616321560000001</v>
+        <v>-9.5863641299999998</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H65" s="5">
-        <v>1642</v>
+        <v>4605.5</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J65" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J65" s="41"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
@@ -4231,12 +4322,12 @@
       <c r="O65"/>
       <c r="P65"/>
     </row>
-    <row r="66" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3">
-        <v>46252.635416666664</v>
+    <row r="66" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>10</v>
@@ -4245,23 +4336,21 @@
         <v>100</v>
       </c>
       <c r="E66" s="4">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="F66" s="4">
-        <v>1.5584415579999999</v>
+        <v>-10.28853148</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="H66" s="5">
-        <v>385</v>
+        <v>123.73</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J66" s="41"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
@@ -4269,56 +4358,51 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B66, $C$2:$C$760, C66, $D$2:$D$760, D66, $E$2:$E$760, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="29">
-        <v>46255</v>
-      </c>
-      <c r="B67" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C67" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D67" s="31">
-        <v>1</v>
-      </c>
-      <c r="E67" s="31">
-        <v>19550</v>
+      <c r="O66"/>
+      <c r="P66"/>
+    </row>
+    <row r="67" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="4">
+        <v>4</v>
+      </c>
+      <c r="E67" s="4">
+        <v>701</v>
       </c>
       <c r="F67" s="4">
-        <v>1.6905071519999999</v>
+        <v>-10.74611663</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H67" s="5">
-        <v>19225</v>
+        <v>785.4</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="44" t="s">
+      <c r="J67" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K67" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="L67" s="27">
-        <v>19992</v>
-      </c>
-      <c r="M67" s="27">
-        <f>ABS((D67*E67)-L67)</f>
-        <v>442</v>
-      </c>
-      <c r="N67" s="28" t="str">
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B67, $C$2:$C$760, C67, $D$2:$D$760, D67, $E$2:$E$760, E67) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O67"/>
       <c r="P67"/>
     </row>
-    <row r="68" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
@@ -4329,13 +4413,13 @@
         <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" s="4">
-        <v>4710</v>
+        <v>4014</v>
       </c>
       <c r="F68" s="4">
-        <v>2.269026164</v>
+        <v>-12.84333949</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>98</v>
@@ -4346,9 +4430,7 @@
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J68" s="41"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
@@ -4451,12 +4533,12 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="3">
-        <v>46252.635416666664</v>
+    <row r="71" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>10</v>
@@ -4465,23 +4547,21 @@
         <v>1</v>
       </c>
       <c r="E71" s="4">
-        <v>13552</v>
+        <v>2752</v>
       </c>
       <c r="F71" s="4">
-        <v>3.0100334449999999</v>
+        <v>-13.35012594</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H71" s="5">
-        <v>13156</v>
+        <v>3176</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J71" s="41"/>
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
@@ -4489,84 +4569,77 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B71, $C$2:$C$760, C71, $D$2:$D$760, D71, $E$2:$E$760, E71) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
-        <v>46275.457638888889</v>
+        <v>46252.688194444447</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E72" s="4">
-        <v>222</v>
+        <v>136.15</v>
       </c>
       <c r="F72" s="4">
-        <v>3.2654200389999999</v>
+        <v>-14.50549451</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="H72" s="5">
-        <v>214.98</v>
+        <v>159.25</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K72" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="L72" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M72" s="18">
-        <f>ABS((D72*E72)-L72)</f>
-        <v>34175</v>
-      </c>
-      <c r="N72" s="10" t="str">
+      <c r="J72" s="41"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B72, $C$2:$C$760, C72, $D$2:$D$760, D72, $E$2:$E$760, E72) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4">
-        <v>2435</v>
+        <v>196</v>
       </c>
       <c r="F73" s="4">
-        <v>3.26547922</v>
+        <v>-14.559721010000001</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H73" s="5">
-        <v>2358</v>
+        <v>229.4</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J73" s="41"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
@@ -4574,8 +4647,8 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B73, $C$2:$C$760, C73, $D$2:$D$760, D73, $E$2:$E$760, E73) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
+      <c r="O73"/>
+      <c r="P73"/>
     </row>
     <row r="74" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
@@ -4673,35 +4746,35 @@
       </c>
       <c r="P75" s="10"/>
     </row>
-    <row r="76" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="3">
-        <v>46252.645138888889</v>
+    <row r="76" spans="1:16" s="35" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E76" s="4">
-        <v>401</v>
+        <v>3914</v>
       </c>
       <c r="F76" s="4">
-        <v>4.1558441559999997</v>
+        <v>-15.014656390000001</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="H76" s="5">
-        <v>385</v>
+        <v>4605.5</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="43" t="s">
+      <c r="J76" s="42" t="s">
         <v>41</v>
       </c>
       <c r="K76" s="17"/>
@@ -4711,51 +4784,42 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B76, $C$2:$C$760, C76, $D$2:$D$760, D76, $E$2:$E$760, E76) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-    </row>
-    <row r="77" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="3">
-        <v>46267.375</v>
+      <c r="O76"/>
+      <c r="P76"/>
+    </row>
+    <row r="77" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D77" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="4">
-        <v>20050</v>
+        <v>2660</v>
       </c>
       <c r="F77" s="4">
-        <v>4.2912873859999996</v>
+        <v>-16.24685139</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H77" s="5">
-        <v>19225</v>
+        <v>3176</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J77" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K77" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="L77" s="18">
-        <v>20350</v>
-      </c>
-      <c r="M77" s="18">
-        <f>ABS((D77*E77)-L77)</f>
-        <v>300</v>
-      </c>
-      <c r="N77" s="10" t="str">
+      <c r="J77" s="41"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
+      <c r="M77" s="17"/>
+      <c r="N77" t="str">
         <f>IF(COUNTIFS( $B$2:$B$760, B77, $C$2:$C$760, C77, $D$2:$D$760, D77, $E$2:$E$760, E77) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
@@ -4894,37 +4958,35 @@
         <v>249</v>
       </c>
     </row>
-    <row r="81" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D81" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E81" s="4">
-        <v>281</v>
+        <v>660</v>
       </c>
       <c r="F81" s="4">
-        <v>4.5192486519999999</v>
+        <v>-16.624557859999999</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H81" s="5">
-        <v>268.85000000000002</v>
+        <v>791.6</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="63" t="s">
-        <v>41</v>
-      </c>
+      <c r="J81" s="63"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
@@ -4932,8 +4994,6 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B81, $C$2:$C$760, C81, $D$2:$D$760, D81, $E$2:$E$760, E81) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O81" s="10"/>
-      <c r="P81" s="26"/>
     </row>
     <row r="82" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="36">
@@ -5035,37 +5095,35 @@
       </c>
       <c r="P83" s="35"/>
     </row>
-    <row r="84" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D84" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E84" s="4">
-        <v>2470</v>
+        <v>2560</v>
       </c>
       <c r="F84" s="4">
-        <v>4.7497879559999996</v>
+        <v>-19.395465990000002</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H84" s="5">
-        <v>2358</v>
+        <v>3176</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J84" s="63" t="s">
-        <v>41</v>
-      </c>
+      <c r="J84" s="63"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
@@ -5073,8 +5131,6 @@
         <f>IF(COUNTIFS( $B$2:$B$760, B84, $C$2:$C$760, C84, $D$2:$D$760, D84, $E$2:$E$760, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O84" s="10"/>
-      <c r="P84" s="25"/>
     </row>
     <row r="85" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
@@ -5118,7 +5174,7 @@
         <v>26610</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B85, $C$2:$C$760, C85, $D$2:$D$760, D85, $E$2:$E$760, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="0">IF(COUNTIFS( $B$2:$B$760, B85, $C$2:$C$760, C85, $D$2:$D$760, D85, $E$2:$E$760, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
@@ -5166,7 +5222,7 @@
         <v>175</v>
       </c>
       <c r="N86" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B86, $C$2:$C$760, C86, $D$2:$D$760, D86, $E$2:$E$760, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O86" s="46" t="s">
@@ -5215,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="N87" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B87, $C$2:$C$760, C87, $D$2:$D$760, D87, $E$2:$E$760, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O87" s="46" t="s">
@@ -5258,7 +5314,7 @@
       <c r="L88" s="18"/>
       <c r="M88" s="18"/>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B88, $C$2:$C$760, C88, $D$2:$D$760, D88, $E$2:$E$760, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="46" t="s">
@@ -5293,7 +5349,7 @@
       <c r="I89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="64" t="s">
+      <c r="J89" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K89" s="18" t="s">
@@ -5303,11 +5359,11 @@
         <v>10400</v>
       </c>
       <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" ref="M89:M106" si="1">ABS((D89*E89)-L89)</f>
         <v>300</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B89, $C$2:$C$760, C89, $D$2:$D$760, D89, $E$2:$E$760, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5349,11 +5405,11 @@
         <v>19730.5</v>
       </c>
       <c r="M90" s="33">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="1"/>
         <v>504.5</v>
       </c>
       <c r="N90" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B90, $C$2:$C$760, C90, $D$2:$D$760, D90, $E$2:$E$760, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O90" s="46" t="s">
@@ -5398,11 +5454,11 @@
         <v>19690</v>
       </c>
       <c r="M91" s="33">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="1"/>
         <v>545</v>
       </c>
       <c r="N91" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B91, $C$2:$C$760, C91, $D$2:$D$760, D91, $E$2:$E$760, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="46" t="s">
@@ -5447,11 +5503,11 @@
         <v>16580</v>
       </c>
       <c r="M92" s="52">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
       <c r="N92" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B92, $C$2:$C$760, C92, $D$2:$D$760, D92, $E$2:$E$760, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="25"/>
@@ -5497,11 +5553,11 @@
         <v>32200</v>
       </c>
       <c r="M93" s="18">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B93, $C$2:$C$760, C93, $D$2:$D$760, D93, $E$2:$E$760, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="10"/>
@@ -5545,11 +5601,11 @@
         <v>17404</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="1"/>
         <v>516</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B94, $C$2:$C$760, C94, $D$2:$D$760, D94, $E$2:$E$760, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5591,11 +5647,11 @@
         <v>9170</v>
       </c>
       <c r="M95" s="33">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B95, $C$2:$C$760, C95, $D$2:$D$760, D95, $E$2:$E$760, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="10"/>
@@ -5639,11 +5695,11 @@
         <v>23450</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B96, $C$2:$C$760, C96, $D$2:$D$760, D96, $E$2:$E$760, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
@@ -5687,11 +5743,11 @@
         <v>8220</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B97, $C$2:$C$760, C97, $D$2:$D$760, D97, $E$2:$E$760, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="46" t="s">
@@ -5736,11 +5792,11 @@
         <v>39300</v>
       </c>
       <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="1"/>
         <v>18850</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B98, $C$2:$C$760, C98, $D$2:$D$760, D98, $E$2:$E$760, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5782,11 +5838,11 @@
         <v>8700</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B99, $C$2:$C$760, C99, $D$2:$D$760, D99, $E$2:$E$760, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="10"/>
@@ -5830,11 +5886,11 @@
         <v>20010</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B100, $C$2:$C$760, C100, $D$2:$D$760, D100, $E$2:$E$760, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P100"/>
@@ -5877,11 +5933,11 @@
         <v>35880</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="1"/>
         <v>26460</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B101, $C$2:$C$760, C101, $D$2:$D$760, D101, $E$2:$E$760, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5923,11 +5979,11 @@
         <v>5905</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="1"/>
         <v>275</v>
       </c>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B102, $C$2:$C$760, C102, $D$2:$D$760, D102, $E$2:$E$760, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5969,11 +6025,11 @@
         <v>20260</v>
       </c>
       <c r="M103" s="18">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B103, $C$2:$C$760, C103, $D$2:$D$760, D103, $E$2:$E$760, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O103"/>
@@ -6017,11 +6073,11 @@
         <v>9170</v>
       </c>
       <c r="M104" s="33">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B104, $C$2:$C$760, C104, $D$2:$D$760, D104, $E$2:$E$760, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6063,11 +6119,11 @@
         <v>32900</v>
       </c>
       <c r="M105" s="33">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="N105" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B105, $C$2:$C$760, C105, $D$2:$D$760, D105, $E$2:$E$760, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O105" s="26"/>
@@ -6110,11 +6166,11 @@
         <v>33200</v>
       </c>
       <c r="M106" s="33">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
       <c r="N106" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B106, $C$2:$C$760, C106, $D$2:$D$760, D106, $E$2:$E$760, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O106" s="10"/>
@@ -6150,7 +6206,7 @@
       </c>
       <c r="J107" s="40"/>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B107, $C$2:$C$760, C107, $D$2:$D$760, D107, $E$2:$E$760, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6192,15 +6248,15 @@
         <v>4852</v>
       </c>
       <c r="M108" s="18">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" ref="M108:M116" si="2">ABS((D108*E108)-L108)</f>
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B108, $C$2:$C$760, C108, $D$2:$D$760, D108, $E$2:$E$760, E108) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
         <v>46280.375914351855</v>
       </c>
@@ -6238,11 +6294,11 @@
         <v>8320</v>
       </c>
       <c r="M109" s="18">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B109, $C$2:$C$760, C109, $D$2:$D$760, D109, $E$2:$E$760, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -6286,11 +6342,11 @@
         <v>3300</v>
       </c>
       <c r="M110" s="18">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B110, $C$2:$C$760, C110, $D$2:$D$760, D110, $E$2:$E$760, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="10"/>
@@ -6334,11 +6390,11 @@
         <v>8480</v>
       </c>
       <c r="M111" s="27">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="2"/>
         <v>280</v>
       </c>
       <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B111, $C$2:$C$760, C111, $D$2:$D$760, D111, $E$2:$E$760, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="46" t="s">
@@ -6383,11 +6439,11 @@
         <v>15075</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="2"/>
         <v>645</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B112, $C$2:$C$760, C112, $D$2:$D$760, D112, $E$2:$E$760, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="46" t="s">
@@ -6432,11 +6488,11 @@
         <v>16755</v>
       </c>
       <c r="M113" s="18">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="2"/>
         <v>295</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B113, $C$2:$C$760, C113, $D$2:$D$760, D113, $E$2:$E$760, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6478,11 +6534,11 @@
         <v>8420</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B114, $C$2:$C$760, C114, $D$2:$D$760, D114, $E$2:$E$760, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6524,11 +6580,11 @@
         <v>14440</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B115, $C$2:$C$760, C115, $D$2:$D$760, D115, $E$2:$E$760, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O115"/>
@@ -6571,11 +6627,11 @@
         <v>73800</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="2"/>
         <v>48320</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B116, $C$2:$C$760, C116, $D$2:$D$760, D116, $E$2:$E$760, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="46" t="s">
@@ -6612,7 +6668,7 @@
       </c>
       <c r="J117" s="40"/>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B117, $C$2:$C$760, C117, $D$2:$D$760, D117, $E$2:$E$760, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6658,7 +6714,7 @@
         <v>150</v>
       </c>
       <c r="N118" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B118, $C$2:$C$760, C118, $D$2:$D$760, D118, $E$2:$E$760, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -6704,7 +6760,7 @@
         <v>250</v>
       </c>
       <c r="N119" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B119, $C$2:$C$760, C119, $D$2:$D$760, D119, $E$2:$E$760, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -6750,7 +6806,7 @@
         <v>300</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B120, $C$2:$C$760, C120, $D$2:$D$760, D120, $E$2:$E$760, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P120" s="19"/>
@@ -6783,7 +6839,7 @@
       <c r="I121" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J121" s="64" t="s">
+      <c r="J121" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K121" s="18" t="s">
@@ -6797,7 +6853,7 @@
         <v>1246</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B121, $C$2:$C$760, C121, $D$2:$D$760, D121, $E$2:$E$760, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="10"/>
@@ -6833,7 +6889,7 @@
       </c>
       <c r="J122" s="40"/>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B122, $C$2:$C$760, C122, $D$2:$D$760, D122, $E$2:$E$760, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="25"/>
@@ -6870,7 +6926,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B123, $C$2:$C$760, C123, $D$2:$D$760, D123, $E$2:$E$760, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6912,11 +6968,11 @@
         <v>39300</v>
       </c>
       <c r="M124" s="18">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" ref="M124:M134" si="3">ABS((D124*E124)-L124)</f>
         <v>18350</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B124, $C$2:$C$760, C124, $D$2:$D$760, D124, $E$2:$E$760, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6958,11 +7014,11 @@
         <v>18800</v>
       </c>
       <c r="M125" s="18">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" si="3"/>
         <v>500</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B125, $C$2:$C$760, C125, $D$2:$D$760, D125, $E$2:$E$760, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="47" t="s">
@@ -7007,11 +7063,11 @@
         <v>10300</v>
       </c>
       <c r="M126" s="18">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B126, $C$2:$C$760, C126, $D$2:$D$760, D126, $E$2:$E$760, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P126" s="35"/>
@@ -7054,11 +7110,11 @@
         <v>33950</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B127, $C$2:$C$760, C127, $D$2:$D$760, D127, $E$2:$E$760, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7100,11 +7156,11 @@
         <v>11320</v>
       </c>
       <c r="M128" s="18">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B128, $C$2:$C$760, C128, $D$2:$D$760, D128, $E$2:$E$760, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -7148,11 +7204,11 @@
         <v>5370</v>
       </c>
       <c r="M129" s="33">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="3"/>
         <v>320</v>
       </c>
       <c r="N129" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B129, $C$2:$C$760, C129, $D$2:$D$760, D129, $E$2:$E$760, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7194,11 +7250,11 @@
         <v>2610</v>
       </c>
       <c r="M130" s="33">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="N130" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B130, $C$2:$C$760, C130, $D$2:$D$760, D130, $E$2:$E$760, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="4">IF(COUNTIFS( $B$2:$B$760, B130, $C$2:$C$760, C130, $D$2:$D$760, D130, $E$2:$E$760, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7240,11 +7296,11 @@
         <v>10249</v>
       </c>
       <c r="M131" s="18">
-        <f>ABS((D131*E131)-L131)</f>
+        <f t="shared" si="3"/>
         <v>4451</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B131, $C$2:$C$760, C131, $D$2:$D$760, D131, $E$2:$E$760, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7286,11 +7342,11 @@
         <v>7578</v>
       </c>
       <c r="M132" s="33">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="N132" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B132, $C$2:$C$760, C132, $D$2:$D$760, D132, $E$2:$E$760, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7332,11 +7388,11 @@
         <v>7578</v>
       </c>
       <c r="M133" s="33">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="N133" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B133, $C$2:$C$760, C133, $D$2:$D$760, D133, $E$2:$E$760, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7378,11 +7434,11 @@
         <v>4968</v>
       </c>
       <c r="M134" s="33">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="N134" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B134, $C$2:$C$760, C134, $D$2:$D$760, D134, $E$2:$E$760, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="35"/>
@@ -7418,7 +7474,7 @@
       </c>
       <c r="J135" s="40"/>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B135, $C$2:$C$760, C135, $D$2:$D$760, D135, $E$2:$E$760, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7454,7 +7510,7 @@
         <v>117</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B136, $C$2:$C$760, C136, $D$2:$D$760, D136, $E$2:$E$760, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7496,11 +7552,11 @@
         <v>17040</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" ref="M137:M142" si="5">ABS((D137*E137)-L137)</f>
         <v>880</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B137, $C$2:$C$760, C137, $D$2:$D$760, D137, $E$2:$E$760, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="46" t="s">
@@ -7545,11 +7601,11 @@
         <v>73800</v>
       </c>
       <c r="M138" s="18">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="5"/>
         <v>47900</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B138, $C$2:$C$760, C138, $D$2:$D$760, D138, $E$2:$E$760, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="46" t="s">
@@ -7594,11 +7650,11 @@
         <v>25300</v>
       </c>
       <c r="M139" s="18">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B139, $C$2:$C$760, C139, $D$2:$D$760, D139, $E$2:$E$760, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="46" t="s">
@@ -7643,11 +7699,11 @@
         <v>12480</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="5"/>
         <v>495</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B140, $C$2:$C$760, C140, $D$2:$D$760, D140, $E$2:$E$760, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="46" t="s">
@@ -7692,11 +7748,11 @@
         <v>34100</v>
       </c>
       <c r="M141" s="18">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="5"/>
         <v>700</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B141, $C$2:$C$760, C141, $D$2:$D$760, D141, $E$2:$E$760, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P141" s="10"/>
@@ -7739,11 +7795,11 @@
         <v>10410</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B142, $C$2:$C$760, C142, $D$2:$D$760, D142, $E$2:$E$760, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="35"/>
@@ -7778,7 +7834,7 @@
       </c>
       <c r="J143" s="40"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B143, $C$2:$C$760, C143, $D$2:$D$760, D143, $E$2:$E$760, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="46" t="s">
@@ -7824,11 +7880,11 @@
         <v>4120</v>
       </c>
       <c r="M144" s="33">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" ref="M144:M158" si="6">ABS((D144*E144)-L144)</f>
         <v>270</v>
       </c>
       <c r="N144" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B144, $C$2:$C$760, C144, $D$2:$D$760, D144, $E$2:$E$760, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="34" t="s">
@@ -7874,11 +7930,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M145" s="33">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="6"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N145" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B145, $C$2:$C$760, C145, $D$2:$D$760, D145, $E$2:$E$760, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="34" t="s">
@@ -7924,11 +7980,11 @@
         <v>14100</v>
       </c>
       <c r="M146" s="18">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B146, $C$2:$C$760, C146, $D$2:$D$760, D146, $E$2:$E$760, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="10"/>
@@ -7972,11 +8028,11 @@
         <v>2899.25</v>
       </c>
       <c r="M147" s="18">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="6"/>
         <v>300.75</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B147, $C$2:$C$760, C147, $D$2:$D$760, D147, $E$2:$E$760, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8018,11 +8074,11 @@
         <v>17150</v>
       </c>
       <c r="M148" s="18">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B148, $C$2:$C$760, C148, $D$2:$D$760, D148, $E$2:$E$760, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8064,11 +8120,11 @@
         <v>8570</v>
       </c>
       <c r="M149" s="33">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B149, $C$2:$C$760, C149, $D$2:$D$760, D149, $E$2:$E$760, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="46" t="s">
@@ -8113,11 +8169,11 @@
         <v>25780</v>
       </c>
       <c r="M150" s="18">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N150" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B150, $C$2:$C$760, C150, $D$2:$D$760, D150, $E$2:$E$760, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="46" t="s">
@@ -8163,11 +8219,11 @@
         <v>18960</v>
       </c>
       <c r="M151" s="18">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="6"/>
         <v>816</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B151, $C$2:$C$760, C151, $D$2:$D$760, D151, $E$2:$E$760, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8209,11 +8265,11 @@
         <v>8049</v>
       </c>
       <c r="M152" s="18">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="6"/>
         <v>800</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B152, $C$2:$C$760, C152, $D$2:$D$760, D152, $E$2:$E$760, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8255,11 +8311,11 @@
         <v>3400</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B153, $C$2:$C$760, C153, $D$2:$D$760, D153, $E$2:$E$760, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8301,11 +8357,11 @@
         <v>9470</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B154, $C$2:$C$760, C154, $D$2:$D$760, D154, $E$2:$E$760, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8347,11 +8403,11 @@
         <v>3810</v>
       </c>
       <c r="M155" s="18">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N155" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B155, $C$2:$C$760, C155, $D$2:$D$760, D155, $E$2:$E$760, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8393,11 +8449,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M156" s="33">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="6"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B156, $C$2:$C$760, C156, $D$2:$D$760, D156, $E$2:$E$760, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="46" t="s">
@@ -8443,11 +8499,11 @@
         <v>25530</v>
       </c>
       <c r="M157" s="18">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N157" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B157, $C$2:$C$760, C157, $D$2:$D$760, D157, $E$2:$E$760, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O157"/>
@@ -8491,11 +8547,11 @@
         <v>14200</v>
       </c>
       <c r="M158" s="18">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B158, $C$2:$C$760, C158, $D$2:$D$760, D158, $E$2:$E$760, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8532,7 +8588,7 @@
       <c r="L159" s="18"/>
       <c r="M159" s="18"/>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B159, $C$2:$C$760, C159, $D$2:$D$760, D159, $E$2:$E$760, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="10"/>
@@ -8580,7 +8636,7 @@
         <v>300</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B160, $C$2:$C$760, C160, $D$2:$D$760, D160, $E$2:$E$760, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="10"/>
@@ -8628,7 +8684,7 @@
         <v>300</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B161, $C$2:$C$760, C161, $D$2:$D$760, D161, $E$2:$E$760, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="46" t="s">
@@ -8678,7 +8734,7 @@
         <v>651</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B162, $C$2:$C$760, C162, $D$2:$D$760, D162, $E$2:$E$760, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8724,7 +8780,7 @@
         <v>47480</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B163, $C$2:$C$760, C163, $D$2:$D$760, D163, $E$2:$E$760, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8770,7 +8826,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B164, $C$2:$C$760, C164, $D$2:$D$760, D164, $E$2:$E$760, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8809,7 +8865,7 @@
         <v>145</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B165, $C$2:$C$760, C165, $D$2:$D$760, D165, $E$2:$E$760, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8855,7 +8911,7 @@
         <v>340</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B166, $C$2:$C$760, C166, $D$2:$D$760, D166, $E$2:$E$760, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8901,7 +8957,7 @@
         <v>240</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B167, $C$2:$C$760, C167, $D$2:$D$760, D167, $E$2:$E$760, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P167" s="26"/>
@@ -8936,7 +8992,7 @@
       </c>
       <c r="J168" s="40"/>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B168, $C$2:$C$760, C168, $D$2:$D$760, D168, $E$2:$E$760, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8972,7 +9028,7 @@
         <v>118</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B169, $C$2:$C$760, C169, $D$2:$D$760, D169, $E$2:$E$760, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9018,7 +9074,7 @@
         <v>140</v>
       </c>
       <c r="N170" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B170, $C$2:$C$760, C170, $D$2:$D$760, D170, $E$2:$E$760, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="P170" s="35"/>
@@ -9065,7 +9121,7 @@
         <v>300</v>
       </c>
       <c r="N171" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B171, $C$2:$C$760, C171, $D$2:$D$760, D171, $E$2:$E$760, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9104,7 +9160,7 @@
       <c r="L172" s="18"/>
       <c r="M172" s="18"/>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B172, $C$2:$C$760, C172, $D$2:$D$760, D172, $E$2:$E$760, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="10"/>
@@ -9145,7 +9201,7 @@
       <c r="L173" s="18"/>
       <c r="M173" s="18"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B173, $C$2:$C$760, C173, $D$2:$D$760, D173, $E$2:$E$760, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="10"/>
@@ -9193,7 +9249,7 @@
         <v>260</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B174, $C$2:$C$760, C174, $D$2:$D$760, D174, $E$2:$E$760, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9239,7 +9295,7 @@
         <v>300</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B175, $C$2:$C$760, C175, $D$2:$D$760, D175, $E$2:$E$760, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9275,7 +9331,7 @@
         <v>118</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B176, $C$2:$C$760, C176, $D$2:$D$760, D176, $E$2:$E$760, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="35"/>
@@ -9310,7 +9366,7 @@
       </c>
       <c r="J177" s="40"/>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B177, $C$2:$C$760, C177, $D$2:$D$760, D177, $E$2:$E$760, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="35"/>
@@ -9357,7 +9413,7 @@
         <v>500</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B178, $C$2:$C$760, C178, $D$2:$D$760, D178, $E$2:$E$760, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="10"/>
@@ -9405,7 +9461,7 @@
         <v>650</v>
       </c>
       <c r="N179" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B179, $C$2:$C$760, C179, $D$2:$D$760, D179, $E$2:$E$760, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="46" t="s">
@@ -9447,7 +9503,7 @@
       <c r="L180" s="52"/>
       <c r="M180" s="52"/>
       <c r="N180" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B180, $C$2:$C$760, C180, $D$2:$D$760, D180, $E$2:$E$760, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="25"/>
@@ -9497,7 +9553,7 @@
         <v>250</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B181, $C$2:$C$760, C181, $D$2:$D$760, D181, $E$2:$E$760, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P181" s="35"/>
@@ -9530,9 +9586,9 @@
       <c r="I182" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J182" s="65"/>
+      <c r="J182" s="40"/>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B182, $C$2:$C$760, C182, $D$2:$D$760, D182, $E$2:$E$760, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9578,7 +9634,7 @@
         <v>300</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B183, $C$2:$C$760, C183, $D$2:$D$760, D183, $E$2:$E$760, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9614,7 +9670,7 @@
         <v>118</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B184, $C$2:$C$760, C184, $D$2:$D$760, D184, $E$2:$E$760, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="46" t="s">
@@ -9663,7 +9719,7 @@
         <v>300</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B185, $C$2:$C$760, C185, $D$2:$D$760, D185, $E$2:$E$760, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="46" t="s">
@@ -9706,7 +9762,7 @@
       <c r="L186" s="18"/>
       <c r="M186" s="18"/>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B186, $C$2:$C$760, C186, $D$2:$D$760, D186, $E$2:$E$760, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="10"/>
@@ -9742,7 +9798,7 @@
       </c>
       <c r="J187" s="40"/>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B187, $C$2:$C$760, C187, $D$2:$D$760, D187, $E$2:$E$760, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="35"/>
@@ -9777,7 +9833,7 @@
       </c>
       <c r="J188" s="40"/>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B188, $C$2:$C$760, C188, $D$2:$D$760, D188, $E$2:$E$760, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9813,7 +9869,7 @@
         <v>118</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B189, $C$2:$C$760, C189, $D$2:$D$760, D189, $E$2:$E$760, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9849,7 +9905,7 @@
         <v>117</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B190, $C$2:$C$760, C190, $D$2:$D$760, D190, $E$2:$E$760, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9890,7 +9946,7 @@
       <c r="L191" s="17"/>
       <c r="M191" s="17"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B191, $C$2:$C$760, C191, $D$2:$D$760, D191, $E$2:$E$760, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="10"/>
@@ -9938,7 +9994,7 @@
         <v>290</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B192, $C$2:$C$760, C192, $D$2:$D$760, D192, $E$2:$E$760, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="10"/>
@@ -9976,7 +10032,7 @@
         <v>118</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B193, $C$2:$C$760, C193, $D$2:$D$760, D193, $E$2:$E$760, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10022,7 +10078,7 @@
         <v>320</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B194, $C$2:$C$760, C194, $D$2:$D$760, D194, $E$2:$E$760, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$760, B194, $C$2:$C$760, C194, $D$2:$D$760, D194, $E$2:$E$760, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10068,7 +10124,7 @@
         <v>448</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B195, $C$2:$C$760, C195, $D$2:$D$760, D195, $E$2:$E$760, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10104,11 +10160,11 @@
         <v>197</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B196, $C$2:$C$760, C196, $D$2:$D$760, D196, $E$2:$E$760, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="36">
         <v>46272.451388888891</v>
       </c>
@@ -10146,17 +10202,17 @@
         <v>8820</v>
       </c>
       <c r="M197" s="33">
-        <f>ABS((D197*E197)-L197)</f>
+        <f t="shared" ref="M197:M203" si="8">ABS((D197*E197)-L197)</f>
         <v>650</v>
       </c>
       <c r="N197" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B197, $C$2:$C$760, C197, $D$2:$D$760, D197, $E$2:$E$760, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="35"/>
       <c r="P197" s="35"/>
     </row>
-    <row r="198" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="36">
         <v>46272.390972222223</v>
       </c>
@@ -10194,11 +10250,11 @@
         <v>36946</v>
       </c>
       <c r="M198" s="33">
-        <f>ABS((D198*E198)-L198)</f>
+        <f t="shared" si="8"/>
         <v>934</v>
       </c>
       <c r="N198" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B198, $C$2:$C$760, C198, $D$2:$D$760, D198, $E$2:$E$760, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="35"/>
@@ -10242,11 +10298,11 @@
         <v>10814</v>
       </c>
       <c r="M199" s="18">
-        <f>ABS((D199*E199)-L199)</f>
+        <f t="shared" si="8"/>
         <v>501</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B199, $C$2:$C$760, C199, $D$2:$D$760, D199, $E$2:$E$760, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="46" t="s">
@@ -10291,11 +10347,11 @@
         <v>5620</v>
       </c>
       <c r="M200" s="33">
-        <f>ABS((D200*E200)-L200)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B200, $C$2:$C$760, C200, $D$2:$D$760, D200, $E$2:$E$760, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P200" s="26"/>
@@ -10338,11 +10394,11 @@
         <v>7200</v>
       </c>
       <c r="M201" s="18">
-        <f>ABS((D201*E201)-L201)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B201, $C$2:$C$760, C201, $D$2:$D$760, D201, $E$2:$E$760, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10384,11 +10440,11 @@
         <v>4170</v>
       </c>
       <c r="M202" s="18">
-        <f>ABS((D202*E202)-L202)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B202, $C$2:$C$760, C202, $D$2:$D$760, D202, $E$2:$E$760, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="10"/>
@@ -10432,11 +10488,11 @@
         <v>14650</v>
       </c>
       <c r="M203" s="18">
-        <f>ABS((D203*E203)-L203)</f>
+        <f t="shared" si="8"/>
         <v>450</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B203, $C$2:$C$760, C203, $D$2:$D$760, D203, $E$2:$E$760, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="10"/>
@@ -10472,7 +10528,7 @@
       </c>
       <c r="J204" s="40"/>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B204, $C$2:$C$760, C204, $D$2:$D$760, D204, $E$2:$E$760, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10508,7 +10564,7 @@
         <v>155</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B205, $C$2:$C$760, C205, $D$2:$D$760, D205, $E$2:$E$760, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10554,7 +10610,7 @@
         <v>646</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B206, $C$2:$C$760, C206, $D$2:$D$760, D206, $E$2:$E$760, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="46" t="s">
@@ -10593,7 +10649,7 @@
         <v>55</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B207, $C$2:$C$760, C207, $D$2:$D$760, D207, $E$2:$E$760, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10629,7 +10685,7 @@
         <v>118</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B208, $C$2:$C$760, C208, $D$2:$D$760, D208, $E$2:$E$760, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10675,7 +10731,7 @@
         <v>800</v>
       </c>
       <c r="N209" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B209, $C$2:$C$760, C209, $D$2:$D$760, D209, $E$2:$E$760, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10721,7 +10777,7 @@
         <v>360</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B210, $C$2:$C$760, C210, $D$2:$D$760, D210, $E$2:$E$760, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10767,7 +10823,7 @@
         <v>1800</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B211, $C$2:$C$760, C211, $D$2:$D$760, D211, $E$2:$E$760, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10803,7 +10859,7 @@
         <v>118</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B212, $C$2:$C$760, C212, $D$2:$D$760, D212, $E$2:$E$760, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10839,7 +10895,7 @@
         <v>117</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B213, $C$2:$C$760, C213, $D$2:$D$760, D213, $E$2:$E$760, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P213" s="35"/>
@@ -10886,7 +10942,7 @@
         <v>300</v>
       </c>
       <c r="N214" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B214, $C$2:$C$760, C214, $D$2:$D$760, D214, $E$2:$E$760, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10932,7 +10988,7 @@
         <v>188</v>
       </c>
       <c r="N215" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B215, $C$2:$C$760, C215, $D$2:$D$760, D215, $E$2:$E$760, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="35"/>
@@ -10980,7 +11036,7 @@
         <v>650</v>
       </c>
       <c r="N216" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B216, $C$2:$C$760, C216, $D$2:$D$760, D216, $E$2:$E$760, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="46" t="s">
@@ -10988,7 +11044,7 @@
       </c>
       <c r="P216" s="35"/>
     </row>
-    <row r="217" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -11030,7 +11086,7 @@
         <v>1000</v>
       </c>
       <c r="N217" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B217, $C$2:$C$760, C217, $D$2:$D$760, D217, $E$2:$E$760, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P217" s="35"/>
@@ -11067,7 +11123,7 @@
         <v>117</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B218, $C$2:$C$760, C218, $D$2:$D$760, D218, $E$2:$E$760, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11113,7 +11169,7 @@
         <v>300</v>
       </c>
       <c r="N219" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B219, $C$2:$C$760, C219, $D$2:$D$760, D219, $E$2:$E$760, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P219" s="10"/>
@@ -11160,7 +11216,7 @@
         <v>253</v>
       </c>
       <c r="N220" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B220, $C$2:$C$760, C220, $D$2:$D$760, D220, $E$2:$E$760, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O220" s="35"/>
@@ -11207,7 +11263,7 @@
         <v>355.5</v>
       </c>
       <c r="N221" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B221, $C$2:$C$760, C221, $D$2:$D$760, D221, $E$2:$E$760, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O221" s="35"/>
@@ -11245,7 +11301,7 @@
         <v>118</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B222, $C$2:$C$760, C222, $D$2:$D$760, D222, $E$2:$E$760, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11279,7 +11335,7 @@
       </c>
       <c r="J223" s="40"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B223, $C$2:$C$760, C223, $D$2:$D$760, D223, $E$2:$E$760, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P223" s="35"/>
@@ -11326,7 +11382,7 @@
         <v>250</v>
       </c>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B224, $C$2:$C$760, C224, $D$2:$D$760, D224, $E$2:$E$760, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11372,7 +11428,7 @@
         <v>650</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B225, $C$2:$C$760, C225, $D$2:$D$760, D225, $E$2:$E$760, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="35"/>
@@ -11407,7 +11463,7 @@
       </c>
       <c r="J226" s="40"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B226, $C$2:$C$760, C226, $D$2:$D$760, D226, $E$2:$E$760, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11453,7 +11509,7 @@
         <v>500</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B227, $C$2:$C$760, C227, $D$2:$D$760, D227, $E$2:$E$760, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="46" t="s">
@@ -11492,7 +11548,7 @@
         <v>118</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B228, $C$2:$C$760, C228, $D$2:$D$760, D228, $E$2:$E$760, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11538,7 +11594,7 @@
         <v>300</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B229, $C$2:$C$760, C229, $D$2:$D$760, D229, $E$2:$E$760, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11574,7 +11630,7 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B230, $C$2:$C$760, C230, $D$2:$D$760, D230, $E$2:$E$760, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11620,7 +11676,7 @@
         <v>527.5</v>
       </c>
       <c r="N231" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B231, $C$2:$C$760, C231, $D$2:$D$760, D231, $E$2:$E$760, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="35"/>
@@ -11663,13 +11719,13 @@
       <c r="L232" s="33"/>
       <c r="M232" s="33"/>
       <c r="N232" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B232, $C$2:$C$760, C232, $D$2:$D$760, D232, $E$2:$E$760, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="35"/>
       <c r="P232" s="35"/>
     </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11711,7 +11767,7 @@
         <v>940</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B233, $C$2:$C$760, C233, $D$2:$D$760, D233, $E$2:$E$760, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11757,7 +11813,7 @@
         <v>400</v>
       </c>
       <c r="N234" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B234, $C$2:$C$760, C234, $D$2:$D$760, D234, $E$2:$E$760, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11803,7 +11859,7 @@
         <v>450</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B235, $C$2:$C$760, C235, $D$2:$D$760, D235, $E$2:$E$760, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11837,7 +11893,7 @@
       </c>
       <c r="J236" s="40"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B236, $C$2:$C$760, C236, $D$2:$D$760, D236, $E$2:$E$760, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11883,7 +11939,7 @@
         <v>300</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B237, $C$2:$C$760, C237, $D$2:$D$760, D237, $E$2:$E$760, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11924,7 +11980,7 @@
       <c r="L238" s="18"/>
       <c r="M238" s="18"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B238, $C$2:$C$760, C238, $D$2:$D$760, D238, $E$2:$E$760, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O238" s="10"/>
@@ -11962,7 +12018,7 @@
         <v>117</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B239, $C$2:$C$760, C239, $D$2:$D$760, D239, $E$2:$E$760, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11996,7 +12052,7 @@
       </c>
       <c r="J240" s="40"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B240, $C$2:$C$760, C240, $D$2:$D$760, D240, $E$2:$E$760, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12032,7 +12088,7 @@
         <v>55</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B241, $C$2:$C$760, C241, $D$2:$D$760, D241, $E$2:$E$760, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12066,7 +12122,7 @@
       </c>
       <c r="J242" s="40"/>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B242, $C$2:$C$760, C242, $D$2:$D$760, D242, $E$2:$E$760, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12100,7 +12156,7 @@
       </c>
       <c r="J243" s="40"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B243, $C$2:$C$760, C243, $D$2:$D$760, D243, $E$2:$E$760, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12136,7 +12192,7 @@
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B244, $C$2:$C$760, C244, $D$2:$D$760, D244, $E$2:$E$760, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="35"/>
@@ -12183,7 +12239,7 @@
         <v>268</v>
       </c>
       <c r="N245" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B245, $C$2:$C$760, C245, $D$2:$D$760, D245, $E$2:$E$760, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12219,7 +12275,7 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B246, $C$2:$C$760, C246, $D$2:$D$760, D246, $E$2:$E$760, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12265,7 +12321,7 @@
         <v>285</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B247, $C$2:$C$760, C247, $D$2:$D$760, D247, $E$2:$E$760, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="10"/>
@@ -12313,7 +12369,7 @@
         <v>726</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B248, $C$2:$C$760, C248, $D$2:$D$760, D248, $E$2:$E$760, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12359,7 +12415,7 @@
         <v>370</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B249, $C$2:$C$760, C249, $D$2:$D$760, D249, $E$2:$E$760, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P249" s="35"/>
@@ -12406,7 +12462,7 @@
         <v>300</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B250, $C$2:$C$760, C250, $D$2:$D$760, D250, $E$2:$E$760, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12440,7 +12496,7 @@
       </c>
       <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B251, $C$2:$C$760, C251, $D$2:$D$760, D251, $E$2:$E$760, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12474,7 +12530,7 @@
       </c>
       <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B252, $C$2:$C$760, C252, $D$2:$D$760, D252, $E$2:$E$760, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12510,11 +12566,11 @@
         <v>118</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B253, $C$2:$C$760, C253, $D$2:$D$760, D253, $E$2:$E$760, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="3">
         <v>46260.375</v>
       </c>
@@ -12556,7 +12612,7 @@
         <v>650</v>
       </c>
       <c r="N254" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B254, $C$2:$C$760, C254, $D$2:$D$760, D254, $E$2:$E$760, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="35"/>
@@ -12596,7 +12652,7 @@
         <v>146</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B255, $C$2:$C$760, C255, $D$2:$D$760, D255, $E$2:$E$760, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12632,7 +12688,7 @@
         <v>117</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B256, $C$2:$C$760, C256, $D$2:$D$760, D256, $E$2:$E$760, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12678,7 +12734,7 @@
         <v>260</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B257, $C$2:$C$760, C257, $D$2:$D$760, D257, $E$2:$E$760, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12724,7 +12780,7 @@
         <v>275</v>
       </c>
       <c r="N258" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B258, $C$2:$C$760, C258, $D$2:$D$760, D258, $E$2:$E$760, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N297" si="9">IF(COUNTIFS( $B$2:$B$760, B258, $C$2:$C$760, C258, $D$2:$D$760, D258, $E$2:$E$760, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12770,7 +12826,7 @@
         <v>250</v>
       </c>
       <c r="N259" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B259, $C$2:$C$760, C259, $D$2:$D$760, D259, $E$2:$E$760, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12804,7 +12860,7 @@
       </c>
       <c r="J260" s="40"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B260, $C$2:$C$760, C260, $D$2:$D$760, D260, $E$2:$E$760, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12850,7 +12906,7 @@
         <v>300</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B261, $C$2:$C$760, C261, $D$2:$D$760, D261, $E$2:$E$760, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12884,11 +12940,11 @@
       </c>
       <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B262, $C$2:$C$760, C262, $D$2:$D$760, D262, $E$2:$E$760, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>46252.6875</v>
       </c>
@@ -12920,7 +12976,7 @@
         <v>118</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B263, $C$2:$C$760, C263, $D$2:$D$760, D263, $E$2:$E$760, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="35"/>
@@ -12955,7 +13011,7 @@
       </c>
       <c r="J264" s="40"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B264, $C$2:$C$760, C264, $D$2:$D$760, D264, $E$2:$E$760, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12989,7 +13045,7 @@
       </c>
       <c r="J265" s="40"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B265, $C$2:$C$760, C265, $D$2:$D$760, D265, $E$2:$E$760, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13035,7 +13091,7 @@
         <v>250</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B266, $C$2:$C$760, C266, $D$2:$D$760, D266, $E$2:$E$760, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P266" s="35"/>
@@ -13070,7 +13126,7 @@
       </c>
       <c r="J267" s="40"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B267, $C$2:$C$760, C267, $D$2:$D$760, D267, $E$2:$E$760, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P267" s="35"/>
@@ -13117,7 +13173,7 @@
         <v>480</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B268, $C$2:$C$760, C268, $D$2:$D$760, D268, $E$2:$E$760, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13151,7 +13207,7 @@
       </c>
       <c r="J269" s="40"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B269, $C$2:$C$760, C269, $D$2:$D$760, D269, $E$2:$E$760, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13187,7 +13243,7 @@
         <v>117</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B270, $C$2:$C$760, C270, $D$2:$D$760, D270, $E$2:$E$760, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13221,7 +13277,7 @@
       </c>
       <c r="J271" s="40"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B271, $C$2:$C$760, C271, $D$2:$D$760, D271, $E$2:$E$760, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13257,7 +13313,7 @@
         <v>118</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B272, $C$2:$C$760, C272, $D$2:$D$760, D272, $E$2:$E$760, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13291,7 +13347,7 @@
       </c>
       <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B273, $C$2:$C$760, C273, $D$2:$D$760, D273, $E$2:$E$760, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13337,7 +13393,7 @@
         <v>300</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B274, $C$2:$C$760, C274, $D$2:$D$760, D274, $E$2:$E$760, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13383,7 +13439,7 @@
         <v>250</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B275, $C$2:$C$760, C275, $D$2:$D$760, D275, $E$2:$E$760, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13419,7 +13475,7 @@
         <v>118</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B276, $C$2:$C$760, C276, $D$2:$D$760, D276, $E$2:$E$760, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13455,7 +13511,7 @@
         <v>118</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B277, $C$2:$C$760, C277, $D$2:$D$760, D277, $E$2:$E$760, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13491,7 +13547,7 @@
         <v>118</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B278, $C$2:$C$760, C278, $D$2:$D$760, D278, $E$2:$E$760, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13525,7 +13581,7 @@
       </c>
       <c r="J279" s="40"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B279, $C$2:$C$760, C279, $D$2:$D$760, D279, $E$2:$E$760, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13559,7 +13615,7 @@
       </c>
       <c r="J280" s="40"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B280, $C$2:$C$760, C280, $D$2:$D$760, D280, $E$2:$E$760, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13593,7 +13649,7 @@
       </c>
       <c r="J281" s="40"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B281, $C$2:$C$760, C281, $D$2:$D$760, D281, $E$2:$E$760, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O281" s="35"/>
@@ -13628,7 +13684,7 @@
       </c>
       <c r="J282" s="40"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B282, $C$2:$C$760, C282, $D$2:$D$760, D282, $E$2:$E$760, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13674,7 +13730,7 @@
         <v>300</v>
       </c>
       <c r="N283" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B283, $C$2:$C$760, C283, $D$2:$D$760, D283, $E$2:$E$760, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13710,11 +13766,11 @@
         <v>117</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B284, $C$2:$C$760, C284, $D$2:$D$760, D284, $E$2:$E$760, E284) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>46252.6875</v>
       </c>
@@ -13749,7 +13805,7 @@
       <c r="L285" s="18"/>
       <c r="M285" s="18"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B285, $C$2:$C$760, C285, $D$2:$D$760, D285, $E$2:$E$760, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O285" s="10"/>
@@ -13788,7 +13844,7 @@
       <c r="L286" s="18"/>
       <c r="M286" s="18"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B286, $C$2:$C$760, C286, $D$2:$D$760, D286, $E$2:$E$760, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O286" s="10"/>
@@ -13824,11 +13880,11 @@
       </c>
       <c r="J287" s="40"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B287, $C$2:$C$760, C287, $D$2:$D$760, D287, $E$2:$E$760, E287) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13858,7 +13914,7 @@
       </c>
       <c r="J288" s="40"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B288, $C$2:$C$760, C288, $D$2:$D$760, D288, $E$2:$E$760, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P288" s="35"/>
@@ -13895,7 +13951,7 @@
         <v>118</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B289, $C$2:$C$760, C289, $D$2:$D$760, D289, $E$2:$E$760, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13931,7 +13987,7 @@
         <v>118</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B290, $C$2:$C$760, C290, $D$2:$D$760, D290, $E$2:$E$760, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13967,11 +14023,11 @@
         <v>55</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B291, $C$2:$C$760, C291, $D$2:$D$760, D291, $E$2:$E$760, E291) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="8" t="s">
         <v>62</v>
       </c>
@@ -14001,7 +14057,7 @@
       </c>
       <c r="J292" s="40"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B292, $C$2:$C$760, C292, $D$2:$D$760, D292, $E$2:$E$760, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14047,11 +14103,11 @@
         <v>250</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B293, $C$2:$C$760, C293, $D$2:$D$760, D293, $E$2:$E$760, E293) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="294" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="8" t="s">
         <v>62</v>
       </c>
@@ -14081,11 +14137,11 @@
       </c>
       <c r="J294" s="40"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B294, $C$2:$C$760, C294, $D$2:$D$760, D294, $E$2:$E$760, E294) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="295" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="8" t="s">
         <v>62</v>
       </c>
@@ -14115,11 +14171,11 @@
       </c>
       <c r="J295" s="40"/>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B295, $C$2:$C$760, C295, $D$2:$D$760, D295, $E$2:$E$760, E295) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -14149,7 +14205,7 @@
       </c>
       <c r="J296" s="40"/>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B296, $C$2:$C$760, C296, $D$2:$D$760, D296, $E$2:$E$760, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="35"/>
@@ -14184,27 +14240,19 @@
       </c>
       <c r="J297" s="40"/>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$760, B297, $C$2:$C$760, C297, $D$2:$D$760, D297, $E$2:$E$760, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P297" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="KERNEXEQ"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P297">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P84">
+      <sortCondition descending="1" ref="F1:F297"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
